--- a/excel/studentContract.xlsx
+++ b/excel/studentContract.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -31,13 +31,13 @@
     <t xml:space="preserve">pasport</t>
   </si>
   <si>
-    <t xml:space="preserve">Ta'lim yo'nalishi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ta'lim turi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">edu_level_uz</t>
+    <t xml:space="preserve">speciality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">study_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">degree</t>
   </si>
   <si>
     <t xml:space="preserve">period</t>
@@ -58,13 +58,13 @@
     <t xml:space="preserve">Telefoni</t>
   </si>
   <si>
-    <t xml:space="preserve">NAMAZOVA (ABDUG'OFUROVA) LUIZA BEKZOD QIZI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AD (AA)2958650 (1225510)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEDAGOGIKA VA PSIXOLOGIYA</t>
+    <t xml:space="preserve">TURG'UNOV RAXMATULLO ROZIQJON O'G'LI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AA7280190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IQTISODIYOT</t>
   </si>
   <si>
     <t xml:space="preserve">SIRTQI</t>
@@ -73,7 +73,7 @@
     <t xml:space="preserve">Bakalavr</t>
   </si>
   <si>
-    <t xml:space="preserve">TOSHKENT VILOYATI, BO'KA TUMANI, JAG'AYBOSHI 6-UY</t>
+    <t xml:space="preserve">ANDIJON VILOYATI, ULUG'NOR TUMANI, SHUKRONA K 8-UY</t>
   </si>
 </sst>
 </file>
@@ -85,11 +85,12 @@
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -110,9 +111,9 @@
       <b val="true"/>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
+      <name val="Times New Roman1"/>
       <family val="0"/>
-      <charset val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <b val="true"/>
@@ -120,21 +121,14 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="4">
@@ -157,7 +151,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -172,6 +166,20 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -198,11 +206,15 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -215,27 +227,31 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -316,128 +332,87 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="33.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="53.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26.28"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
-        <v>11112221</v>
-      </c>
-      <c r="B2" s="5" t="s">
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="n">
+        <v>22000939</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="G2" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H2" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" s="7" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>35490</v>
-      </c>
-      <c r="K2" s="9" t="s">
+      <c r="H2" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" s="9" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="J2" s="10" t="n">
+        <v>33685</v>
+      </c>
+      <c r="K2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="6" t="n">
-        <v>770179794</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
-        <v>22000021</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I3" s="7" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="J3" s="8" t="n">
-        <v>35490</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" s="6" t="n">
-        <v>770179794</v>
+      <c r="L2" s="7" t="n">
+        <v>999880322</v>
       </c>
     </row>
   </sheetData>
